--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jul-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jul-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>16762.27</v>
+        <v>16921.49</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>50344.22</v>
+        <v>50822.44</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>43830.24</v>
+        <v>44246.58</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>6515.12</v>
+        <v>6540.55</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5701.41</v>
+        <v>5758.75</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>36632.76</v>
+        <v>37001.19</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9987.85</v>
+        <v>10087.86</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>19672.92</v>
+        <v>19773.17</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>17052.64</v>
+        <v>17139.53</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>10219.36</v>
+        <v>10271.43</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>9606.58</v>
+        <v>9643.969999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>25467.24</v>
+        <v>25566.37</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>11364.08</v>
+        <v>11408.32</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>11789.85</v>
+        <v>11835.75</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6410.92</v>
+        <v>6378.44</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7770.35</v>
+        <v>7730.99</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7524.39</v>
+        <v>7540.43</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>51102.57</v>
+        <v>51211.49</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>29532.37</v>
+        <v>29595.31</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5713.29</v>
+        <v>5725.47</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>54532.14</v>
+        <v>54648.37</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>19515.96</v>
+        <v>19557.55</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>17420.96</v>
+        <v>17534.53</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>6410.91</v>
+        <v>6452.7</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>63067.34</v>
+        <v>63478.5</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>38411.35</v>
+        <v>38661.76</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8655.68</v>
+        <v>8675.530000000001</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>10324.67</v>
+        <v>10348.34</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>21993.99</v>
+        <v>22141.2</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>36806.76</v>
+        <v>37053.12</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>9730.540000000001</v>
+        <v>9795.67</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>8856.33</v>
+        <v>8918.309999999999</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>6091.59</v>
+        <v>6134.22</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>11005.71</v>
+        <v>11082.73</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>18197.5</v>
+        <v>18324.85</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>25263.51</v>
+        <v>25208.54</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>10421.99</v>
+        <v>10399.31</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>7745.5</v>
+        <v>7728.65</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>10396.3</v>
+        <v>10373.68</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>30718.59</v>
+        <v>30657.01</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>200006.3</v>
+        <v>198848.63</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>63550.15</v>
+        <v>63182.31</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>8218.59</v>
+        <v>8085.96</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>7988.99</v>
+        <v>7860.07</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>15787.28</v>
+        <v>15534.15</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>21179.27</v>
+        <v>20839.69</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>39255.8</v>
+        <v>38626.39</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>12678.94</v>
+        <v>12531.41</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>8936.32</v>
+        <v>8832.34</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>7793.42</v>
+        <v>7702.74</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>23091.21</v>
+        <v>22822.53</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>17649.08</v>
+        <v>17443.73</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>33634.43</v>
+        <v>33243.07</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>6398.11</v>
+        <v>6323.67</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>8155.24</v>
+        <v>8110.03</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>14500.04</v>
+        <v>14419.65</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>5560.51</v>
+        <v>5529.68</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>35810.32</v>
+        <v>35611.79</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>7133.97</v>
+        <v>7094.42</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>6410.91</v>
+        <v>6379.39</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jul-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jul-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jul-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jul-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCAC</t>
+          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARRO</t>
+          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE TALCAHUANO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>MUSEO HISTÓRICO NACIONAL</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA SAN ANTONIO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3533,12 +3533,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - IX Zona Araucania</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARRO</t>
+          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DIVISIÓN DE BIENESTAR SOCIAL</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jul-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jul-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1257,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1322,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1387,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1452,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1578,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1765,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1891,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1956,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2326,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2391,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2517,11 @@
           <t>77.367.722-0</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2582,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2647,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2773,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2899,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2964,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3029,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3277,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3342,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3529,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3655,11 @@
           <t>77.351.814-9</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3781,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3846,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3972,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4159,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4224,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jul-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jul-2026.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
